--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260626.xlsx
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>105,141,708</t>
+          <t>1,213,892</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,213,892</t>
+          <t>105,141,708</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>3,804,114</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>3,804,114</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
